--- a/data/dividends_info_20260527.xlsx
+++ b/data/dividends_info_20260527.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>60.7400016784668</v>
+        <v>57.95000076293945</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1481725345949509</v>
+        <v>0.1553062964885366</v>
       </c>
       <c r="J2" t="n">
         <v>292</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>55.29999923706055</v>
+        <v>55</v>
       </c>
       <c r="I3" t="n">
-        <v>1.265822802273891</v>
+        <v>1.272727272727272</v>
       </c>
       <c r="J3" t="n">
         <v>271</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.199999809265137</v>
+        <v>9.060000419616699</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6521739265643809</v>
+        <v>0.6622516249567504</v>
       </c>
       <c r="J4" t="n">
         <v>201</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>60.7400016784668</v>
+        <v>57.95000076293945</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1481725345949509</v>
+        <v>0.1553062964885366</v>
       </c>
       <c r="J6" t="n">
         <v>201</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.075000047683716</v>
+        <v>2.069999933242798</v>
       </c>
       <c r="I7" t="n">
-        <v>3.710843288218411</v>
+        <v>3.719806883248261</v>
       </c>
       <c r="J7" t="n">
         <v>180</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>22.70000076293945</v>
+        <v>22.52000045776367</v>
       </c>
       <c r="I8" t="n">
-        <v>1.189427272799075</v>
+        <v>1.198934256268715</v>
       </c>
       <c r="J8" t="n">
         <v>180</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.75</v>
+        <v>5.659999847412109</v>
       </c>
       <c r="I9" t="n">
-        <v>3.478260869565217</v>
+        <v>3.533568999855095</v>
       </c>
       <c r="J9" t="n">
         <v>173</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7.099999904632568</v>
+        <v>7</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8450704338862249</v>
+        <v>0.8571428571428572</v>
       </c>
       <c r="J10" t="n">
         <v>145</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.960000038146973</v>
+        <v>4.949999809265137</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7661290263658259</v>
+        <v>0.7676767972571169</v>
       </c>
       <c r="J13" t="n">
         <v>124</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>22.69499969482422</v>
+        <v>22.52000045776367</v>
       </c>
       <c r="I14" t="n">
-        <v>1.189689374887173</v>
+        <v>1.198934256268715</v>
       </c>
       <c r="J14" t="n">
         <v>117</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>60.7400016784668</v>
+        <v>57.95000076293945</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1481725345949509</v>
+        <v>0.1553062964885366</v>
       </c>
       <c r="J15" t="n">
         <v>117</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5.199999809265137</v>
+        <v>5.380000114440918</v>
       </c>
       <c r="I16" t="n">
-        <v>5.7692309808449</v>
+        <v>5.576208059824095</v>
       </c>
       <c r="J16" t="n">
         <v>110</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4.960000038146973</v>
+        <v>4.949999809265137</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7661290263658259</v>
+        <v>0.7676767972571169</v>
       </c>
       <c r="J18" t="n">
         <v>68</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.889999866485596</v>
+        <v>5.900000095367432</v>
       </c>
       <c r="I19" t="n">
-        <v>4.244482269388714</v>
+        <v>4.237288067101817</v>
       </c>
       <c r="J19" t="n">
         <v>61</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>9.657999992370605</v>
+        <v>9.590000152587891</v>
       </c>
       <c r="I20" t="n">
-        <v>2.69206875342088</v>
+        <v>2.711157412545382</v>
       </c>
       <c r="J20" t="n">
         <v>54</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>15.15999984741211</v>
+        <v>15</v>
       </c>
       <c r="I21" t="n">
-        <v>3.957783680996692</v>
+        <v>4</v>
       </c>
       <c r="J21" t="n">
         <v>54</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>3.634000062942505</v>
+        <v>3.70799994468689</v>
       </c>
       <c r="I22" t="n">
-        <v>6.053934952930701</v>
+        <v>5.933117672108736</v>
       </c>
       <c r="J22" t="n">
         <v>54</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>6.329999923706055</v>
+        <v>6.269999980926514</v>
       </c>
       <c r="I24" t="n">
-        <v>1.579778850004354</v>
+        <v>1.594896336590149</v>
       </c>
       <c r="J24" t="n">
         <v>54</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>18.79999923706055</v>
+        <v>18.89999961853027</v>
       </c>
       <c r="I25" t="n">
-        <v>2.000000081163775</v>
+        <v>1.989418029571574</v>
       </c>
       <c r="J25" t="n">
         <v>54</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>4.324999809265137</v>
+        <v>4.28000020980835</v>
       </c>
       <c r="I26" t="n">
-        <v>2.774566596348342</v>
+        <v>2.803738180315963</v>
       </c>
       <c r="J26" t="n">
         <v>47</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2.680000066757202</v>
+        <v>2.660000085830688</v>
       </c>
       <c r="I28" t="n">
-        <v>5.597014785954832</v>
+        <v>5.639097562403148</v>
       </c>
       <c r="J28" t="n">
         <v>47</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2.160000085830688</v>
+        <v>2.240000009536743</v>
       </c>
       <c r="I29" t="n">
-        <v>3.935185028814982</v>
+        <v>3.794642840987262</v>
       </c>
       <c r="J29" t="n">
         <v>40</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>4.400000095367432</v>
+        <v>4.369999885559082</v>
       </c>
       <c r="I30" t="n">
-        <v>1.590909056427066</v>
+        <v>1.601830705564068</v>
       </c>
       <c r="J30" t="n">
         <v>40</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>31.45000076293945</v>
+        <v>31</v>
       </c>
       <c r="I31" t="n">
-        <v>0.4769475242008876</v>
+        <v>0.4838709677419355</v>
       </c>
       <c r="J31" t="n">
         <v>40</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>5.75</v>
+        <v>5.800000190734863</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6956521739130435</v>
+        <v>0.6896551497342619</v>
       </c>
       <c r="J32" t="n">
         <v>33</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>23.18000030517578</v>
+        <v>22.89999961853027</v>
       </c>
       <c r="I33" t="n">
-        <v>4.098360601780828</v>
+        <v>4.148471684826042</v>
       </c>
       <c r="J33" t="n">
         <v>26</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>31.20000076293945</v>
+        <v>30.5</v>
       </c>
       <c r="I34" t="n">
-        <v>0.6249999847167582</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="J34" t="n">
         <v>26</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1.799999952316284</v>
+        <v>1.870000004768372</v>
       </c>
       <c r="I35" t="n">
-        <v>1.833333381900082</v>
+        <v>1.764705877853063</v>
       </c>
       <c r="J35" t="n">
         <v>26</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>5.340000152587891</v>
+        <v>5.304999828338623</v>
       </c>
       <c r="I36" t="n">
-        <v>5.430711455306965</v>
+        <v>5.466541175946086</v>
       </c>
       <c r="J36" t="n">
         <v>26</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>3.880000114440918</v>
+        <v>3.878000020980835</v>
       </c>
       <c r="I37" t="n">
-        <v>4.123711218576985</v>
+        <v>4.125838038534418</v>
       </c>
       <c r="J37" t="n">
         <v>26</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>2.766000032424927</v>
+        <v>2.747999906539917</v>
       </c>
       <c r="I38" t="n">
-        <v>5.010845928244283</v>
+        <v>5.043668293807007</v>
       </c>
       <c r="J38" t="n">
         <v>26</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>52.91999816894531</v>
+        <v>51.65000152587891</v>
       </c>
       <c r="I39" t="n">
-        <v>1.190476231667179</v>
+        <v>1.21974826987051</v>
       </c>
       <c r="J39" t="n">
         <v>26</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>5.465000152587891</v>
+        <v>5.485000133514404</v>
       </c>
       <c r="I40" t="n">
-        <v>2.561756561593224</v>
+        <v>2.552415616994667</v>
       </c>
       <c r="J40" t="n">
         <v>26</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>25.26000022888184</v>
+        <v>25.20000076293945</v>
       </c>
       <c r="I42" t="n">
-        <v>3.365003928337757</v>
+        <v>3.373015770896555</v>
       </c>
       <c r="J42" t="n">
         <v>26</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>60.7400016784668</v>
+        <v>57.95000076293945</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1481725345949509</v>
+        <v>0.1553062964885366</v>
       </c>
       <c r="J43" t="n">
         <v>26</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1.350000023841858</v>
+        <v>1.379999995231628</v>
       </c>
       <c r="I44" t="n">
-        <v>0.7407407276587887</v>
+        <v>0.7246376836632911</v>
       </c>
       <c r="J44" t="n">
         <v>26</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>6.309999942779541</v>
+        <v>6.26800012588501</v>
       </c>
       <c r="I45" t="n">
-        <v>2.873217141744343</v>
+        <v>2.892469629208907</v>
       </c>
       <c r="J45" t="n">
         <v>26</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>9</v>
+        <v>8.869999885559082</v>
       </c>
       <c r="I46" t="n">
-        <v>2.888888888888889</v>
+        <v>2.931228899149101</v>
       </c>
       <c r="J46" t="n">
         <v>26</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>9.947999954223633</v>
+        <v>9.869999885559082</v>
       </c>
       <c r="I47" t="n">
-        <v>2.784479305133027</v>
+        <v>2.806484328386691</v>
       </c>
       <c r="J47" t="n">
         <v>26</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1.095000028610229</v>
+        <v>1.065000057220459</v>
       </c>
       <c r="I48" t="n">
-        <v>1.232876680116087</v>
+        <v>1.26760556569674</v>
       </c>
       <c r="J48" t="n">
         <v>19</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>3.043999910354614</v>
+        <v>3.032000064849854</v>
       </c>
       <c r="I49" t="n">
-        <v>3.613666335068499</v>
+        <v>3.627968260134166</v>
       </c>
       <c r="J49" t="n">
         <v>19</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>3.240000009536743</v>
+        <v>3.210000038146973</v>
       </c>
       <c r="I51" t="n">
-        <v>4.93827159040277</v>
+        <v>4.984423616778607</v>
       </c>
       <c r="J51" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0.875</v>
+        <v>0.8500000238418579</v>
       </c>
       <c r="I52" t="n">
-        <v>2.857142857142857</v>
+        <v>2.94117638809046</v>
       </c>
       <c r="J52" t="n">
         <v>12</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>29.04999923706055</v>
+        <v>28.95000076293945</v>
       </c>
       <c r="I53" t="n">
-        <v>3.820998379180393</v>
+        <v>3.834196790146459</v>
       </c>
       <c r="J53" t="n">
         <v>8</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>0.9309999942779541</v>
+        <v>0.9150000214576721</v>
       </c>
       <c r="I54" t="n">
-        <v>3.222341588011156</v>
+        <v>3.278688447701616</v>
       </c>
       <c r="J54" t="n">
         <v>5</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>2.309999942779541</v>
+        <v>2.349999904632568</v>
       </c>
       <c r="I58" t="n">
-        <v>7.792207985226717</v>
+        <v>7.659574778925095</v>
       </c>
       <c r="J58" t="n">
         <v>-2</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>8.149999618530273</v>
+        <v>8.050000190734863</v>
       </c>
       <c r="I59" t="n">
-        <v>3.68098176738443</v>
+        <v>3.726707986234393</v>
       </c>
       <c r="J59" t="n">
         <v>-2</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>15.03999996185303</v>
+        <v>15.07999992370605</v>
       </c>
       <c r="I60" t="n">
-        <v>1.662234046769228</v>
+        <v>1.657824942074404</v>
       </c>
       <c r="J60" t="n">
         <v>-2</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>3.609999895095825</v>
+        <v>3.630000114440918</v>
       </c>
       <c r="I61" t="n">
-        <v>0.8310249548969494</v>
+        <v>0.8264462549368407</v>
       </c>
       <c r="J61" t="n">
         <v>-2</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>4.099999904632568</v>
+        <v>4.110000133514404</v>
       </c>
       <c r="I62" t="n">
-        <v>3.658536670464694</v>
+        <v>3.649634917937024</v>
       </c>
       <c r="J62" t="n">
         <v>-2</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>13.44999980926514</v>
+        <v>13.39999961853027</v>
       </c>
       <c r="I63" t="n">
-        <v>4.312267719144966</v>
+        <v>4.328358332174453</v>
       </c>
       <c r="J63" t="n">
         <v>-2</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>2.279999971389771</v>
+        <v>2.259999990463257</v>
       </c>
       <c r="I64" t="n">
-        <v>4.561403566010001</v>
+        <v>4.601769930922964</v>
       </c>
       <c r="J64" t="n">
         <v>-9</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>10.89500045776367</v>
+        <v>10.77000045776367</v>
       </c>
       <c r="I65" t="n">
-        <v>2.661771342958951</v>
+        <v>2.692664695208534</v>
       </c>
       <c r="J65" t="n">
         <v>-9</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>2.075000047683716</v>
+        <v>2.069999933242798</v>
       </c>
       <c r="I66" t="n">
-        <v>3.710843288218411</v>
+        <v>3.719806883248261</v>
       </c>
       <c r="J66" t="n">
         <v>-9</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>38.70999908447266</v>
+        <v>38.72000122070312</v>
       </c>
       <c r="I67" t="n">
-        <v>4.236631461605579</v>
+        <v>4.235537056551308</v>
       </c>
       <c r="J67" t="n">
         <v>-9</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>35.72000122070312</v>
+        <v>35.34000015258789</v>
       </c>
       <c r="I68" t="n">
-        <v>5.599103951992058</v>
+        <v>5.659309539797903</v>
       </c>
       <c r="J68" t="n">
         <v>-9</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>42.22000122070312</v>
+        <v>41.68999862670898</v>
       </c>
       <c r="I70" t="n">
-        <v>0.3516342863751523</v>
+        <v>0.3561045931646735</v>
       </c>
       <c r="J70" t="n">
         <v>-9</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>19.8799991607666</v>
+        <v>19.98999977111816</v>
       </c>
       <c r="I71" t="n">
-        <v>4.627766794958575</v>
+        <v>4.602301203270793</v>
       </c>
       <c r="J71" t="n">
         <v>-9</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>11.5600004196167</v>
+        <v>11.71000003814697</v>
       </c>
       <c r="I72" t="n">
-        <v>2.595155615140949</v>
+        <v>2.561912886615779</v>
       </c>
       <c r="J72" t="n">
         <v>-9</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>83.86000061035156</v>
+        <v>82.94000244140625</v>
       </c>
       <c r="I73" t="n">
-        <v>1.240162166027487</v>
+        <v>1.253918458387698</v>
       </c>
       <c r="J73" t="n">
         <v>-9</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>46.15000152587891</v>
+        <v>46.04000091552734</v>
       </c>
       <c r="I74" t="n">
-        <v>1.516793015938408</v>
+        <v>1.520416998436504</v>
       </c>
       <c r="J74" t="n">
         <v>-9</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>55.25</v>
+        <v>55</v>
       </c>
       <c r="I75" t="n">
-        <v>3.981900452488688</v>
+        <v>4</v>
       </c>
       <c r="J75" t="n">
         <v>-9</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>8.866999626159668</v>
+        <v>8.892000198364258</v>
       </c>
       <c r="I76" t="n">
-        <v>9.698883909533549</v>
+        <v>9.671614719016793</v>
       </c>
       <c r="J76" t="n">
         <v>-9</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>11.66600036621094</v>
+        <v>11.70199966430664</v>
       </c>
       <c r="I77" t="n">
-        <v>4.800274150701792</v>
+        <v>4.785506888263791</v>
       </c>
       <c r="J77" t="n">
         <v>-9</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>2.170000076293945</v>
+        <v>2.150000095367432</v>
       </c>
       <c r="I78" t="n">
-        <v>1.843317907541938</v>
+        <v>1.860465033754525</v>
       </c>
       <c r="J78" t="n">
         <v>-9</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>9.159999847412109</v>
+        <v>9.119999885559082</v>
       </c>
       <c r="I79" t="n">
-        <v>3.275109224862664</v>
+        <v>3.289473725487981</v>
       </c>
       <c r="J79" t="n">
         <v>-9</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>2.230000019073486</v>
+        <v>2.25</v>
       </c>
       <c r="I80" t="n">
-        <v>4.843049285931015</v>
+        <v>4.8</v>
       </c>
       <c r="J80" t="n">
         <v>-9</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>90.69999694824219</v>
+        <v>88.80000305175781</v>
       </c>
       <c r="I81" t="n">
-        <v>2.271223891193222</v>
+        <v>2.319819740095405</v>
       </c>
       <c r="J81" t="n">
         <v>-9</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>15.34000015258789</v>
+        <v>15.19999980926514</v>
       </c>
       <c r="I82" t="n">
-        <v>4.889178569359228</v>
+        <v>4.934210588231973</v>
       </c>
       <c r="J82" t="n">
         <v>-9</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>14.51000022888184</v>
+        <v>14.52000045776367</v>
       </c>
       <c r="I83" t="n">
-        <v>2.067539595229341</v>
+        <v>2.066115637342102</v>
       </c>
       <c r="J83" t="n">
         <v>-9</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>52</v>
+        <v>50.59999847412109</v>
       </c>
       <c r="I84" t="n">
-        <v>1.634615384615385</v>
+        <v>1.679841947890027</v>
       </c>
       <c r="J84" t="n">
         <v>-9</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>35.45999908447266</v>
+        <v>35.18000030517578</v>
       </c>
       <c r="I85" t="n">
-        <v>2.397067179768205</v>
+        <v>2.41614551627774</v>
       </c>
       <c r="J85" t="n">
         <v>-9</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>66.51999664306641</v>
+        <v>65.5</v>
       </c>
       <c r="I86" t="n">
-        <v>1.954299557433161</v>
+        <v>1.984732824427481</v>
       </c>
       <c r="J86" t="n">
         <v>-9</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>7.039999961853027</v>
+        <v>7.079999923706055</v>
       </c>
       <c r="I87" t="n">
-        <v>8.522727318908558</v>
+        <v>8.474576362508314</v>
       </c>
       <c r="J87" t="n">
         <v>-9</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>6.150000095367432</v>
+        <v>6.5</v>
       </c>
       <c r="I88" t="n">
-        <v>7.642276304256217</v>
+        <v>7.230769230769231</v>
       </c>
       <c r="J88" t="n">
         <v>-9</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>5.75</v>
+        <v>5.659999847412109</v>
       </c>
       <c r="I89" t="n">
-        <v>3.478260869565217</v>
+        <v>3.533568999855095</v>
       </c>
       <c r="J89" t="n">
         <v>-9</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>23.28000068664551</v>
+        <v>22.94000053405762</v>
       </c>
       <c r="I90" t="n">
-        <v>4.295532519351027</v>
+        <v>4.35919780610014</v>
       </c>
       <c r="J90" t="n">
         <v>-9</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>4.53000020980835</v>
+        <v>4.610000133514404</v>
       </c>
       <c r="I91" t="n">
-        <v>4.746136645523378</v>
+        <v>4.663774268398906</v>
       </c>
       <c r="J91" t="n">
         <v>-9</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>22.69499969482422</v>
+        <v>22.52000045776367</v>
       </c>
       <c r="I92" t="n">
-        <v>1.189689374887173</v>
+        <v>1.198934256268715</v>
       </c>
       <c r="J92" t="n">
         <v>-9</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>9.220000267028809</v>
+        <v>9.420000076293945</v>
       </c>
       <c r="I93" t="n">
-        <v>2.169197334139026</v>
+        <v>2.123142233335149</v>
       </c>
       <c r="J93" t="n">
         <v>-9</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>8.729999542236328</v>
+        <v>8.800000190734863</v>
       </c>
       <c r="I94" t="n">
-        <v>2.749141037623928</v>
+        <v>2.727272668160684</v>
       </c>
       <c r="J94" t="n">
         <v>-9</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>21.1200008392334</v>
+        <v>21.18000030517578</v>
       </c>
       <c r="I95" t="n">
-        <v>3.740530154394989</v>
+        <v>3.729933846162159</v>
       </c>
       <c r="J95" t="n">
         <v>-9</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>5.239999771118164</v>
+        <v>5.28000020980835</v>
       </c>
       <c r="I96" t="n">
-        <v>1.774809237828549</v>
+        <v>1.761363566373337</v>
       </c>
       <c r="J96" t="n">
         <v>-9</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>7.099999904632568</v>
+        <v>7</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8450704338862249</v>
+        <v>0.8571428571428572</v>
       </c>
       <c r="J97" t="n">
         <v>-9</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>36.72000122070312</v>
+        <v>36.40000152587891</v>
       </c>
       <c r="I98" t="n">
-        <v>0.9531590097079471</v>
+        <v>0.9615384212310112</v>
       </c>
       <c r="J98" t="n">
         <v>-9</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>13.10000038146973</v>
+        <v>13</v>
       </c>
       <c r="I101" t="n">
-        <v>1.526717512794159</v>
+        <v>1.538461538461539</v>
       </c>
       <c r="J101" t="n">
         <v>-9</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>8.090000152587891</v>
+        <v>7.90500020980835</v>
       </c>
       <c r="I102" t="n">
-        <v>1.273176737420105</v>
+        <v>1.302972767441548</v>
       </c>
       <c r="J102" t="n">
         <v>-9</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>5.781000137329102</v>
+        <v>5.789999961853027</v>
       </c>
       <c r="I103" t="n">
-        <v>3.286628532892277</v>
+        <v>3.281519883450786</v>
       </c>
       <c r="J103" t="n">
         <v>-9</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>10.14500045776367</v>
+        <v>10.11499977111816</v>
       </c>
       <c r="I104" t="n">
-        <v>4.258255106035042</v>
+        <v>4.270884921159465</v>
       </c>
       <c r="J104" t="n">
         <v>-9</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>25.39999961853027</v>
+        <v>25.44000053405762</v>
       </c>
       <c r="I105" t="n">
-        <v>1.732283490583217</v>
+        <v>1.729559712119318</v>
       </c>
       <c r="J105" t="n">
         <v>-9</v>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>1.070000052452087</v>
+        <v>1.090000033378601</v>
       </c>
       <c r="I106" t="n">
-        <v>2.803738180315963</v>
+        <v>2.752293493699352</v>
       </c>
       <c r="J106" t="n">
         <v>-9</v>
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>7.21999979019165</v>
+        <v>7.050000190734863</v>
       </c>
       <c r="I107" t="n">
-        <v>6.509695480026102</v>
+        <v>6.666666486302734</v>
       </c>
       <c r="J107" t="n">
         <v>-9</v>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>54.84000015258789</v>
+        <v>54.65999984741211</v>
       </c>
       <c r="I108" t="n">
-        <v>2.552881101576609</v>
+        <v>2.561287969096625</v>
       </c>
       <c r="J108" t="n">
         <v>-9</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>3.486999988555908</v>
+        <v>3.5</v>
       </c>
       <c r="I109" t="n">
-        <v>8.603384025941473</v>
+        <v>8.571428571428571</v>
       </c>
       <c r="J109" t="n">
         <v>-9</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>23.25</v>
+        <v>23.20000076293945</v>
       </c>
       <c r="I112" t="n">
-        <v>3.010752688172043</v>
+        <v>3.017241280087396</v>
       </c>
       <c r="J112" t="n">
         <v>-9</v>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>2.380000114440918</v>
+        <v>2.339999914169312</v>
       </c>
       <c r="I113" t="n">
-        <v>1.47058816458174</v>
+        <v>1.495726550589419</v>
       </c>
       <c r="J113" t="n">
         <v>-9</v>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>5.599999904632568</v>
+        <v>5.579999923706055</v>
       </c>
       <c r="I114" t="n">
-        <v>5.892857243211904</v>
+        <v>5.913978575484007</v>
       </c>
       <c r="J114" t="n">
         <v>-9</v>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>0.8889999985694885</v>
+        <v>0.890999972820282</v>
       </c>
       <c r="I115" t="n">
-        <v>7.874015760701766</v>
+        <v>7.85634142933013</v>
       </c>
       <c r="J115" t="n">
         <v>-9</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>51.34999847412109</v>
+        <v>51.15000152587891</v>
       </c>
       <c r="I116" t="n">
-        <v>1.382668006032793</v>
+        <v>1.388074249891824</v>
       </c>
       <c r="J116" t="n">
         <v>-9</v>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>105.4000015258789</v>
+        <v>103.3000030517578</v>
       </c>
       <c r="I117" t="n">
-        <v>1.280834896068321</v>
+        <v>1.306873146289832</v>
       </c>
       <c r="J117" t="n">
         <v>-9</v>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>7.139999866485596</v>
+        <v>7.119999885559082</v>
       </c>
       <c r="I118" t="n">
-        <v>1.120448200223526</v>
+        <v>1.123595523677711</v>
       </c>
       <c r="J118" t="n">
         <v>-9</v>
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>4.181000232696533</v>
+        <v>4.096000194549561</v>
       </c>
       <c r="I120" t="n">
-        <v>4.066012689273606</v>
+        <v>4.150390427867033</v>
       </c>
       <c r="J120" t="n">
         <v>-9</v>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>7.300000190734863</v>
+        <v>7.349999904632568</v>
       </c>
       <c r="I121" t="n">
-        <v>4.068493044383087</v>
+        <v>4.040816378960854</v>
       </c>
       <c r="J121" t="n">
         <v>-9</v>
@@ -6163,10 +6163,10 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>56.79999923706055</v>
+        <v>57.59999847412109</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7922535317683358</v>
+        <v>0.7812500206960578</v>
       </c>
       <c r="J122" t="n">
         <v>-9</v>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.679999828338623</v>
+        <v>5.559999942779541</v>
       </c>
       <c r="I123" t="n">
-        <v>0.704225373395827</v>
+        <v>0.7194244678355752</v>
       </c>
       <c r="J123" t="n">
         <v>-9</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>37.31999969482422</v>
+        <v>37.43999862670898</v>
       </c>
       <c r="I124" t="n">
-        <v>2.813504846157919</v>
+        <v>2.80448728235516</v>
       </c>
       <c r="J124" t="n">
         <v>-9</v>
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>1.450000047683716</v>
+        <v>1.5</v>
       </c>
       <c r="I125" t="n">
-        <v>3.44827574867131</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="J125" t="n">
         <v>-9</v>
@@ -6351,10 +6351,10 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>18.8799991607666</v>
+        <v>18.10000038146973</v>
       </c>
       <c r="I126" t="n">
-        <v>2.012711953873681</v>
+        <v>2.099447469564881</v>
       </c>
       <c r="J126" t="n">
         <v>-9</v>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>26.20999908447266</v>
+        <v>25.93000030517578</v>
       </c>
       <c r="I127" t="n">
-        <v>2.289202674392508</v>
+        <v>2.313922070722986</v>
       </c>
       <c r="J127" t="n">
         <v>-9</v>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>35.25</v>
+        <v>35.34999847412109</v>
       </c>
       <c r="I128" t="n">
-        <v>0.9929078014184396</v>
+        <v>0.9900990526385079</v>
       </c>
       <c r="J128" t="n">
         <v>-9</v>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>2.904999971389771</v>
+        <v>2.859999895095825</v>
       </c>
       <c r="I130" t="n">
-        <v>0.3442340825640675</v>
+        <v>0.3496503624754485</v>
       </c>
       <c r="J130" t="n">
         <v>-9</v>
@@ -6586,10 +6586,10 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>21.70999908447266</v>
+        <v>21.69000053405762</v>
       </c>
       <c r="I131" t="n">
-        <v>5.158913160899405</v>
+        <v>5.163669766818941</v>
       </c>
       <c r="J131" t="n">
         <v>-9</v>
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>9.279999732971191</v>
+        <v>9.220000267028809</v>
       </c>
       <c r="I133" t="n">
-        <v>2.801724218549686</v>
+        <v>2.819956534380734</v>
       </c>
       <c r="J133" t="n">
         <v>-9</v>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>2.209000110626221</v>
+        <v>2.200000047683716</v>
       </c>
       <c r="I134" t="n">
-        <v>4.178361040182756</v>
+        <v>4.195454454520519</v>
       </c>
       <c r="J134" t="n">
         <v>-9</v>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>9.180000305175781</v>
+        <v>9.279999732971191</v>
       </c>
       <c r="I135" t="n">
-        <v>3.812636038831788</v>
+        <v>3.771551832663038</v>
       </c>
       <c r="J135" t="n">
         <v>-16</v>
@@ -6868,10 +6868,10 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>6.199999809265137</v>
+        <v>6.349999904632568</v>
       </c>
       <c r="I137" t="n">
-        <v>4.838709826275912</v>
+        <v>4.72440951977241</v>
       </c>
       <c r="J137" t="n">
         <v>-16</v>
@@ -6915,10 +6915,10 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>11.80000019073486</v>
+        <v>11.60000038146973</v>
       </c>
       <c r="I138" t="n">
-        <v>1.694915226840727</v>
+        <v>1.724137874335655</v>
       </c>
       <c r="J138" t="n">
         <v>-16</v>
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>9.199999809265137</v>
+        <v>9.060000419616699</v>
       </c>
       <c r="I139" t="n">
-        <v>0.6521739265643809</v>
+        <v>0.6622516249567504</v>
       </c>
       <c r="J139" t="n">
         <v>-16</v>
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>18.79999923706055</v>
+        <v>18.92000007629395</v>
       </c>
       <c r="I140" t="n">
-        <v>2.659574576015658</v>
+        <v>2.642706120421645</v>
       </c>
       <c r="J140" t="n">
         <v>-16</v>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>2.180000066757202</v>
+        <v>2.220000028610229</v>
       </c>
       <c r="I141" t="n">
-        <v>2.752293493699352</v>
+        <v>2.702702667871647</v>
       </c>
       <c r="J141" t="n">
         <v>-16</v>
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>15.4399995803833</v>
+        <v>15.10000038146973</v>
       </c>
       <c r="I142" t="n">
-        <v>3.238342056921141</v>
+        <v>3.311258194493725</v>
       </c>
       <c r="J142" t="n">
         <v>-16</v>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>3.579999923706055</v>
+        <v>3.660000085830688</v>
       </c>
       <c r="I143" t="n">
-        <v>2.79329614891385</v>
+        <v>2.73224037308468</v>
       </c>
       <c r="J143" t="n">
         <v>-16</v>
@@ -7197,10 +7197,10 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>3.130000114440918</v>
+        <v>3.119999885559082</v>
       </c>
       <c r="I144" t="n">
-        <v>3.514376868310379</v>
+        <v>3.525641154960772</v>
       </c>
       <c r="J144" t="n">
         <v>-16</v>
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>4.849999904632568</v>
+        <v>4.690000057220459</v>
       </c>
       <c r="I146" t="n">
-        <v>1.958762925113854</v>
+        <v>2.025586329231348</v>
       </c>
       <c r="J146" t="n">
         <v>-16</v>
@@ -7479,10 +7479,10 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>7.360000133514404</v>
+        <v>7.320000171661377</v>
       </c>
       <c r="I150" t="n">
-        <v>2.989130380558157</v>
+        <v>3.005464410393148</v>
       </c>
       <c r="J150" t="n">
         <v>-16</v>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>24.79999923706055</v>
+        <v>23.85000038146973</v>
       </c>
       <c r="I151" t="n">
-        <v>2.459677495023589</v>
+        <v>2.557651950705795</v>
       </c>
       <c r="J151" t="n">
         <v>-23</v>
@@ -7620,10 +7620,10 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>11.69999980926514</v>
+        <v>11.55000019073486</v>
       </c>
       <c r="I153" t="n">
-        <v>5.982906080440066</v>
+        <v>6.060605960522177</v>
       </c>
       <c r="J153" t="n">
         <v>-23</v>
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>9.170000076293945</v>
+        <v>9.149999618530273</v>
       </c>
       <c r="I154" t="n">
-        <v>5.567066474947277</v>
+        <v>5.579235205279708</v>
       </c>
       <c r="J154" t="n">
         <v>-23</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>7.699999809265137</v>
+        <v>7.510000228881836</v>
       </c>
       <c r="I155" t="n">
-        <v>3.506493593352023</v>
+        <v>3.595206281907135</v>
       </c>
       <c r="J155" t="n">
         <v>-23</v>
@@ -7761,10 +7761,10 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>6.679999828338623</v>
+        <v>6.605000019073486</v>
       </c>
       <c r="I156" t="n">
-        <v>5.239521092728054</v>
+        <v>5.29901588174554</v>
       </c>
       <c r="J156" t="n">
         <v>-23</v>
@@ -7808,10 +7808,10 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>42</v>
+        <v>42.59999847412109</v>
       </c>
       <c r="I157" t="n">
-        <v>2.619047619047619</v>
+        <v>2.582159716902888</v>
       </c>
       <c r="J157" t="n">
         <v>-23</v>
@@ -7855,10 +7855,10 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>17.25</v>
+        <v>17.29999923706055</v>
       </c>
       <c r="I158" t="n">
-        <v>4.347826086956522</v>
+        <v>4.335260306794285</v>
       </c>
       <c r="J158" t="n">
         <v>-23</v>
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>11</v>
+        <v>10.85000038146973</v>
       </c>
       <c r="I159" t="n">
-        <v>3.909090909090909</v>
+        <v>3.963133501215166</v>
       </c>
       <c r="J159" t="n">
         <v>-23</v>
@@ -7949,10 +7949,10 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>4.510000228881836</v>
+        <v>4.539999961853027</v>
       </c>
       <c r="I160" t="n">
-        <v>3.325942181541518</v>
+        <v>3.30396478547054</v>
       </c>
       <c r="J160" t="n">
         <v>-23</v>
@@ -7996,10 +7996,10 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>12.46000003814697</v>
+        <v>12.22000026702881</v>
       </c>
       <c r="I161" t="n">
-        <v>1.582415725492426</v>
+        <v>1.613494236428032</v>
       </c>
       <c r="J161" t="n">
         <v>-23</v>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>29</v>
+        <v>28.5</v>
       </c>
       <c r="I162" t="n">
-        <v>3.793103448275863</v>
+        <v>3.859649122807018</v>
       </c>
       <c r="J162" t="n">
         <v>-23</v>
@@ -8090,10 +8090,10 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>66.59999847412109</v>
+        <v>66.09999847412109</v>
       </c>
       <c r="I163" t="n">
-        <v>0.7057057218741963</v>
+        <v>0.7110438893338407</v>
       </c>
       <c r="J163" t="n">
         <v>-23</v>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>87</v>
+        <v>86.30000305175781</v>
       </c>
       <c r="I164" t="n">
-        <v>1.379310344827586</v>
+        <v>1.390498212706097</v>
       </c>
       <c r="J164" t="n">
         <v>-23</v>
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>23.45000076293945</v>
+        <v>22.95000076293945</v>
       </c>
       <c r="I165" t="n">
-        <v>1.1513858900453</v>
+        <v>1.176470549125238</v>
       </c>
       <c r="J165" t="n">
         <v>-23</v>
@@ -8231,10 +8231,10 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>10.19999980926514</v>
+        <v>10.25</v>
       </c>
       <c r="I166" t="n">
-        <v>3.725490265743223</v>
+        <v>3.707317073170731</v>
       </c>
       <c r="J166" t="n">
         <v>-23</v>
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>33.09999847412109</v>
+        <v>32.90000152587891</v>
       </c>
       <c r="I167" t="n">
-        <v>0.9063444526577609</v>
+        <v>0.9118540610523137</v>
       </c>
       <c r="J167" t="n">
         <v>-23</v>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>0.1700000017881393</v>
+        <v>0.1695999950170517</v>
       </c>
       <c r="I168" t="n">
-        <v>4.117647015512197</v>
+        <v>4.127358611830275</v>
       </c>
       <c r="J168" t="n">
         <v>-30</v>
@@ -8372,10 +8372,10 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>6.820000171661377</v>
+        <v>6.920000076293945</v>
       </c>
       <c r="I169" t="n">
-        <v>2.346040996667943</v>
+        <v>2.312138702832054</v>
       </c>
       <c r="J169" t="n">
         <v>-30</v>
@@ -8419,10 +8419,10 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>2.015000104904175</v>
+        <v>2.029999971389771</v>
       </c>
       <c r="I170" t="n">
-        <v>3.225806283672186</v>
+        <v>3.201970488477394</v>
       </c>
       <c r="J170" t="n">
         <v>-30</v>
@@ -8466,10 +8466,10 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>8.579999923706055</v>
+        <v>8.329999923706055</v>
       </c>
       <c r="I171" t="n">
-        <v>2.913752939662204</v>
+        <v>3.001200507679883</v>
       </c>
       <c r="J171" t="n">
         <v>-30</v>
@@ -10688,350 +10688,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>BEEWIZE</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CIRCLE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CLASS EDITORI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>COFLE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Cogefeed S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Cube Labs S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>E-NOVIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>ErreDue S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ErreDue S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Estrima S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>MEVIM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>OSAI Automation System S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>SIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Sanlorenzo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Softlab S.p.A.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>TALEA GROUP</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>TESMEC S.p.A.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Tenax International S.p.A.</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>